--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK L.E MUZZLELOADER.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK L.E MUZZLELOADER.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -653,7 +658,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -726,7 +732,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -799,7 +806,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -872,7 +880,8 @@
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -945,7 +954,8 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -1014,7 +1024,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1087,7 +1098,8 @@
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1160,7 +1172,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -1233,7 +1246,8 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -1306,7 +1320,8 @@
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -1379,7 +1394,8 @@
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -1452,7 +1468,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -1525,7 +1542,8 @@
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -1598,7 +1616,8 @@
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -1671,7 +1690,8 @@
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -1744,7 +1764,8 @@
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -1817,7 +1838,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1890,7 +1912,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -1963,7 +1986,8 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2036,7 +2060,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -2109,7 +2134,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -2182,7 +2208,8 @@
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -2255,7 +2282,8 @@
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -2328,7 +2356,8 @@
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -2401,7 +2430,8 @@
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2474,7 +2504,8 @@
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -2547,7 +2578,8 @@
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2620,7 +2652,8 @@
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -2693,7 +2726,8 @@
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2766,7 +2800,8 @@
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2839,7 +2874,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2912,7 +2948,8 @@
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -2985,7 +3022,8 @@
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3058,7 +3096,8 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -3131,7 +3170,8 @@
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -3204,7 +3244,8 @@
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3277,7 +3318,8 @@
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -3350,7 +3392,8 @@
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
